--- a/research/traditional_assets/database/data/argentina/argentina_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_hotel_gaming.xlsx
@@ -587,116 +587,110 @@
           <t>Hotel/Gaming</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.0103</v>
+      </c>
       <c r="G2">
-        <v>-0.2628230616302187</v>
+        <v>0.06112185686653772</v>
       </c>
       <c r="H2">
-        <v>-0.5506958250497018</v>
+        <v>-0.102321083172147</v>
       </c>
       <c r="I2">
-        <v>-0.4845577789422007</v>
+        <v>-0.0001932460747751649</v>
       </c>
       <c r="J2">
-        <v>-0.4845577789422007</v>
+        <v>-0.0001932460747751649</v>
       </c>
       <c r="K2">
-        <v>-120.8</v>
+        <v>-65.8</v>
       </c>
       <c r="L2">
-        <v>-0.4803180914512922</v>
+        <v>-0.1272727272727273</v>
       </c>
       <c r="M2">
-        <v>207.17</v>
+        <v>17.37</v>
       </c>
       <c r="N2">
-        <v>0.3251255492780916</v>
+        <v>0.0511183048852266</v>
       </c>
       <c r="O2">
-        <v>-1.714983443708609</v>
+        <v>-0.2639817629179332</v>
       </c>
       <c r="P2">
-        <v>8.470000000000001</v>
+        <v>7.37</v>
       </c>
       <c r="Q2">
-        <v>0.01329252981795355</v>
+        <v>0.02168922895821071</v>
       </c>
       <c r="R2">
-        <v>-0.0701158940397351</v>
+        <v>-0.1120060790273556</v>
       </c>
       <c r="S2">
-        <v>198.7</v>
+        <v>10</v>
       </c>
       <c r="T2">
-        <v>0.9591157020804171</v>
+        <v>0.5757052389176741</v>
       </c>
       <c r="U2">
-        <v>263.2</v>
+        <v>222.7</v>
       </c>
       <c r="V2">
-        <v>0.4130571249215316</v>
+        <v>0.6553855208946439</v>
       </c>
       <c r="W2">
-        <v>-1.001658374792703</v>
+        <v>4.217948717948718</v>
       </c>
       <c r="X2">
-        <v>0.1738706498448895</v>
+        <v>0.2582194134970804</v>
       </c>
       <c r="Y2">
-        <v>-1.175529024637593</v>
-      </c>
-      <c r="Z2">
-        <v>-1.890997448653269</v>
-      </c>
-      <c r="AA2">
-        <v>0.9162975237047961</v>
+        <v>3.959729304451638</v>
       </c>
       <c r="AB2">
-        <v>0.1688795773376691</v>
-      </c>
-      <c r="AC2">
-        <v>0.747417946367127</v>
+        <v>0.241289546460416</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>33.4</v>
       </c>
       <c r="AE2">
-        <v>28.08140701981737</v>
+        <v>18.8495411032938</v>
       </c>
       <c r="AF2">
-        <v>44.58140701981737</v>
+        <v>52.2495411032938</v>
       </c>
       <c r="AG2">
-        <v>-218.6185929801826</v>
+        <v>-170.4504588967062</v>
       </c>
       <c r="AH2">
-        <v>0.06538959050627428</v>
+        <v>0.1332728026061572</v>
       </c>
       <c r="AI2">
-        <v>0.2463314201935436</v>
+        <v>0.5016780731801167</v>
       </c>
       <c r="AJ2">
-        <v>-0.5222845289203978</v>
+        <v>-1.006500860800921</v>
       </c>
       <c r="AK2">
-        <v>2.658992145886963</v>
+        <v>1.437788267401148</v>
       </c>
       <c r="AL2">
-        <v>20.3</v>
+        <v>33.3</v>
       </c>
       <c r="AM2">
-        <v>20.3</v>
+        <v>27.33</v>
       </c>
       <c r="AN2">
-        <v>-0.1773240193444385</v>
+        <v>0.8789473684210526</v>
       </c>
       <c r="AO2">
-        <v>-6.152709359605911</v>
+        <v>-0.106006006006006</v>
       </c>
       <c r="AP2">
-        <v>2.349474400646777</v>
+        <v>-4.485538392018584</v>
       </c>
       <c r="AQ2">
-        <v>-6.152709359605911</v>
+        <v>-0.1291620929381632</v>
       </c>
     </row>
     <row r="3">
@@ -715,116 +709,110 @@
           <t>Hotel/Gaming</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.0103</v>
+      </c>
       <c r="G3">
-        <v>-0.2628230616302187</v>
+        <v>0.06112185686653772</v>
       </c>
       <c r="H3">
-        <v>-0.5506958250497018</v>
+        <v>-0.102321083172147</v>
       </c>
       <c r="I3">
-        <v>-0.4845577789422007</v>
+        <v>-0.0001932460747751649</v>
       </c>
       <c r="J3">
-        <v>-0.4845577789422007</v>
+        <v>-0.0001932460747751649</v>
       </c>
       <c r="K3">
-        <v>-120.8</v>
+        <v>-65.8</v>
       </c>
       <c r="L3">
-        <v>-0.4803180914512922</v>
+        <v>-0.1272727272727273</v>
       </c>
       <c r="M3">
-        <v>207.17</v>
+        <v>17.37</v>
       </c>
       <c r="N3">
-        <v>0.3251255492780916</v>
+        <v>0.0511183048852266</v>
       </c>
       <c r="O3">
-        <v>-1.714983443708609</v>
+        <v>-0.2639817629179332</v>
       </c>
       <c r="P3">
-        <v>8.470000000000001</v>
+        <v>7.37</v>
       </c>
       <c r="Q3">
-        <v>0.01329252981795355</v>
+        <v>0.02168922895821071</v>
       </c>
       <c r="R3">
-        <v>-0.0701158940397351</v>
+        <v>-0.1120060790273556</v>
       </c>
       <c r="S3">
-        <v>198.7</v>
+        <v>10</v>
       </c>
       <c r="T3">
-        <v>0.9591157020804171</v>
+        <v>0.5757052389176741</v>
       </c>
       <c r="U3">
-        <v>263.2</v>
+        <v>222.7</v>
       </c>
       <c r="V3">
-        <v>0.4130571249215316</v>
+        <v>0.6553855208946439</v>
       </c>
       <c r="W3">
-        <v>-1.001658374792703</v>
+        <v>4.217948717948718</v>
       </c>
       <c r="X3">
-        <v>0.1738706498448895</v>
+        <v>0.2582194134970804</v>
       </c>
       <c r="Y3">
-        <v>-1.175529024637593</v>
-      </c>
-      <c r="Z3">
-        <v>-1.890997448653269</v>
-      </c>
-      <c r="AA3">
-        <v>0.9162975237047961</v>
+        <v>3.959729304451638</v>
       </c>
       <c r="AB3">
-        <v>0.1688795773376691</v>
-      </c>
-      <c r="AC3">
-        <v>0.747417946367127</v>
+        <v>0.241289546460416</v>
       </c>
       <c r="AD3">
-        <v>16.5</v>
+        <v>33.4</v>
       </c>
       <c r="AE3">
-        <v>28.08140701981737</v>
+        <v>18.8495411032938</v>
       </c>
       <c r="AF3">
-        <v>44.58140701981737</v>
+        <v>52.2495411032938</v>
       </c>
       <c r="AG3">
-        <v>-218.6185929801826</v>
+        <v>-170.4504588967062</v>
       </c>
       <c r="AH3">
-        <v>0.06538959050627428</v>
+        <v>0.1332728026061572</v>
       </c>
       <c r="AI3">
-        <v>0.2463314201935436</v>
+        <v>0.5016780731801167</v>
       </c>
       <c r="AJ3">
-        <v>-0.5222845289203978</v>
+        <v>-1.006500860800921</v>
       </c>
       <c r="AK3">
-        <v>2.658992145886963</v>
+        <v>1.437788267401148</v>
       </c>
       <c r="AL3">
-        <v>20.3</v>
+        <v>33.3</v>
       </c>
       <c r="AM3">
-        <v>20.3</v>
+        <v>27.33</v>
       </c>
       <c r="AN3">
-        <v>-0.1773240193444385</v>
+        <v>0.8789473684210526</v>
       </c>
       <c r="AO3">
-        <v>-6.152709359605911</v>
+        <v>-0.106006006006006</v>
       </c>
       <c r="AP3">
-        <v>2.349474400646777</v>
+        <v>-4.485538392018584</v>
       </c>
       <c r="AQ3">
-        <v>-6.152709359605911</v>
+        <v>-0.1291620929381632</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/argentina/argentina_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_hotel_gaming.xlsx
@@ -588,109 +588,109 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0103</v>
+        <v>0.0363</v>
+      </c>
+      <c r="E2">
+        <v>-0.161</v>
       </c>
       <c r="G2">
-        <v>0.06112185686653772</v>
+        <v>0.2140762463343108</v>
       </c>
       <c r="H2">
-        <v>-0.102321083172147</v>
+        <v>0.05371199259144929</v>
       </c>
       <c r="I2">
-        <v>-0.0001932460747751649</v>
+        <v>0.08025148096890986</v>
       </c>
       <c r="J2">
-        <v>-0.0001932460747751649</v>
+        <v>0.07906777162461844</v>
       </c>
       <c r="K2">
-        <v>-65.8</v>
+        <v>11.8</v>
       </c>
       <c r="L2">
-        <v>-0.1272727272727273</v>
+        <v>0.01821268714307764</v>
       </c>
       <c r="M2">
-        <v>17.37</v>
+        <v>8.24</v>
       </c>
       <c r="N2">
-        <v>0.0511183048852266</v>
+        <v>0.01318610977756441</v>
       </c>
       <c r="O2">
-        <v>-0.2639817629179332</v>
+        <v>0.6983050847457627</v>
       </c>
       <c r="P2">
-        <v>7.37</v>
+        <v>8.24</v>
       </c>
       <c r="Q2">
-        <v>0.02168922895821071</v>
+        <v>0.01318610977756441</v>
       </c>
       <c r="R2">
-        <v>-0.1120060790273556</v>
+        <v>0.6983050847457627</v>
       </c>
       <c r="S2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.5757052389176741</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>222.7</v>
+        <v>221.7</v>
       </c>
       <c r="V2">
-        <v>0.6553855208946439</v>
+        <v>0.3547767642822852</v>
       </c>
       <c r="W2">
-        <v>4.217948717948718</v>
+        <v>-0.1081576535288726</v>
       </c>
       <c r="X2">
-        <v>0.2582194134970804</v>
+        <v>0.2126936687949302</v>
       </c>
       <c r="Y2">
-        <v>3.959729304451638</v>
+        <v>-0.3208513223238029</v>
       </c>
       <c r="AB2">
-        <v>0.241289546460416</v>
+        <v>0.205996722030555</v>
       </c>
       <c r="AD2">
-        <v>33.4</v>
+        <v>30.7</v>
       </c>
       <c r="AE2">
-        <v>18.8495411032938</v>
+        <v>16.87532740121654</v>
       </c>
       <c r="AF2">
-        <v>52.2495411032938</v>
+        <v>47.57532740121654</v>
       </c>
       <c r="AG2">
-        <v>-170.4504588967062</v>
+        <v>-174.1246725987834</v>
       </c>
       <c r="AH2">
-        <v>0.1332728026061572</v>
+        <v>0.07074657680761549</v>
       </c>
       <c r="AI2">
-        <v>0.5016780731801167</v>
+        <v>0.4480827002438932</v>
       </c>
       <c r="AJ2">
-        <v>-1.006500860800921</v>
+        <v>-0.3862781789825028</v>
       </c>
       <c r="AK2">
-        <v>1.437788267401148</v>
+        <v>1.50725095065638</v>
       </c>
       <c r="AL2">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>27.33</v>
+        <v>-22.7</v>
       </c>
       <c r="AN2">
-        <v>0.8789473684210526</v>
-      </c>
-      <c r="AO2">
-        <v>-0.106006006006006</v>
+        <v>0.3309259458876792</v>
       </c>
       <c r="AP2">
-        <v>-4.485538392018584</v>
+        <v>-1.876950227431103</v>
       </c>
       <c r="AQ2">
-        <v>-0.1291620929381632</v>
+        <v>-2.162995594713657</v>
       </c>
     </row>
     <row r="3">
@@ -710,109 +710,109 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0103</v>
+        <v>0.0363</v>
+      </c>
+      <c r="E3">
+        <v>-0.161</v>
       </c>
       <c r="G3">
-        <v>0.06112185686653772</v>
+        <v>0.2140762463343108</v>
       </c>
       <c r="H3">
-        <v>-0.102321083172147</v>
+        <v>0.05371199259144929</v>
       </c>
       <c r="I3">
-        <v>-0.0001932460747751649</v>
+        <v>0.08025148096890986</v>
       </c>
       <c r="J3">
-        <v>-0.0001932460747751649</v>
+        <v>0.07906777162461844</v>
       </c>
       <c r="K3">
-        <v>-65.8</v>
+        <v>11.8</v>
       </c>
       <c r="L3">
-        <v>-0.1272727272727273</v>
+        <v>0.01821268714307764</v>
       </c>
       <c r="M3">
-        <v>17.37</v>
+        <v>8.24</v>
       </c>
       <c r="N3">
-        <v>0.0511183048852266</v>
+        <v>0.01318610977756441</v>
       </c>
       <c r="O3">
-        <v>-0.2639817629179332</v>
+        <v>0.6983050847457627</v>
       </c>
       <c r="P3">
-        <v>7.37</v>
+        <v>8.24</v>
       </c>
       <c r="Q3">
-        <v>0.02168922895821071</v>
+        <v>0.01318610977756441</v>
       </c>
       <c r="R3">
-        <v>-0.1120060790273556</v>
+        <v>0.6983050847457627</v>
       </c>
       <c r="S3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.5757052389176741</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>222.7</v>
+        <v>221.7</v>
       </c>
       <c r="V3">
-        <v>0.6553855208946439</v>
+        <v>0.3547767642822852</v>
       </c>
       <c r="W3">
-        <v>4.217948717948718</v>
+        <v>-0.1081576535288726</v>
       </c>
       <c r="X3">
-        <v>0.2582194134970804</v>
+        <v>0.2126936687949302</v>
       </c>
       <c r="Y3">
-        <v>3.959729304451638</v>
+        <v>-0.3208513223238029</v>
       </c>
       <c r="AB3">
-        <v>0.241289546460416</v>
+        <v>0.205996722030555</v>
       </c>
       <c r="AD3">
-        <v>33.4</v>
+        <v>30.7</v>
       </c>
       <c r="AE3">
-        <v>18.8495411032938</v>
+        <v>16.87532740121654</v>
       </c>
       <c r="AF3">
-        <v>52.2495411032938</v>
+        <v>47.57532740121654</v>
       </c>
       <c r="AG3">
-        <v>-170.4504588967062</v>
+        <v>-174.1246725987834</v>
       </c>
       <c r="AH3">
-        <v>0.1332728026061572</v>
+        <v>0.07074657680761549</v>
       </c>
       <c r="AI3">
-        <v>0.5016780731801167</v>
+        <v>0.4480827002438932</v>
       </c>
       <c r="AJ3">
-        <v>-1.006500860800921</v>
+        <v>-0.3862781789825028</v>
       </c>
       <c r="AK3">
-        <v>1.437788267401148</v>
+        <v>1.50725095065638</v>
       </c>
       <c r="AL3">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>27.33</v>
+        <v>-22.7</v>
       </c>
       <c r="AN3">
-        <v>0.8789473684210526</v>
-      </c>
-      <c r="AO3">
-        <v>-0.106006006006006</v>
+        <v>0.3309259458876792</v>
       </c>
       <c r="AP3">
-        <v>-4.485538392018584</v>
+        <v>-1.876950227431103</v>
       </c>
       <c r="AQ3">
-        <v>-0.1291620929381632</v>
+        <v>-2.162995594713657</v>
       </c>
     </row>
   </sheetData>
